--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:16:11-03:00</t>
+    <t>2026-08-24T11:43:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T11:43:54-03:00</t>
+    <t>2026-09-15T15:40:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:40:41-03:00</t>
+    <t>2026-09-23T09:07:03-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:07:03-03:00</t>
+    <t>2026-09-30T18:22:16-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:22:16-03:00</t>
+    <t>2026-10-06T15:47:25-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T15:47:25-03:00</t>
+    <t>2026-10-07T20:38:46-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T20:38:46-03:00</t>
+    <t>2026-10-08T20:36:58-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:36:58-03:00</t>
+    <t>2026-10-14T17:05:02-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T17:05:02-03:00</t>
+    <t>2026-10-19T10:41:45-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T10:41:45-03:00</t>
+    <t>2026-10-20T16:57:20-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:57:20-03:00</t>
+    <t>2026-10-21T08:58:18-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T08:58:18-03:00</t>
+    <t>2026-10-21T11:27:45-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRTurno.xlsx
+++ b/output/StructureDefinition-BRTurno.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:27:45-03:00</t>
+    <t>2026-10-21T12:30:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
